--- a/data/trans_bre/P1801_2016_2023-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1801_2016_2023-Estudios-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,2</t>
+          <t>8,28</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 12,82</t>
+          <t>4,0; 12,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 10,66</t>
+          <t>4,21; 13,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 23,22</t>
+          <t>6,62; 23,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 19,07</t>
+          <t>7,13; 25,13</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,88</t>
+          <t>7,03</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,1; 13,19</t>
+          <t>7,45; 14,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 14,95</t>
+          <t>3,9; 10,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,97; 31,68</t>
+          <t>16,55; 33,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,39; 32,19</t>
+          <t>8,46; 24,17</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>6,9</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 18,47</t>
+          <t>5,86; 17,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 9,87</t>
+          <t>1,98; 12,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,16; 46,49</t>
+          <t>12,95; 46,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 18,84</t>
+          <t>3,4; 24,01</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>7,89</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 13,35</t>
+          <t>8,12; 13,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 10,68</t>
+          <t>5,61; 10,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,2; 29,77</t>
+          <t>16,93; 29,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 21,15</t>
+          <t>11,33; 22,29</t>
         </is>
       </c>
     </row>
